--- a/data/trans_dic/P1806_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,86</t>
+          <t>0,57; 2,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,84</t>
+          <t>2,17; 4,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,04</t>
+          <t>1,58; 3,03</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,04</t>
+          <t>0,44; 1,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,05</t>
+          <t>2,26; 4,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,6</t>
+          <t>1,25; 2,57</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,61</t>
+          <t>2,39; 5,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,03</t>
+          <t>2,34; 7,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,61</t>
+          <t>2,89; 5,64</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,0</t>
+          <t>2,58; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,0</t>
+          <t>5,84; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,72</t>
+          <t>4,83; 6,76</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,96</t>
+          <t>1,7; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,62</t>
+          <t>3,95; 5,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,16</t>
+          <t>3,14; 4,12</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3367; 11835</t>
+          <t>3593; 12931</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15517; 32695</t>
+          <t>14697; 32420</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20158; 39820</t>
+          <t>20731; 39672</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5898; 24323</t>
+          <t>5236; 23654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21963; 38846</t>
+          <t>21659; 38865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27740; 55839</t>
+          <t>26822; 55210</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16825; 39554</t>
+          <t>16876; 40138</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23174; 65578</t>
+          <t>21813; 66458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45226; 91820</t>
+          <t>47337; 92377</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24223; 46323</t>
+          <t>23914; 47475</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65460; 98499</t>
+          <t>63903; 97241</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97465; 135787</t>
+          <t>97683; 136690</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>60157; 102574</t>
+          <t>58876; 98977</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>145653; 205827</t>
+          <t>144518; 207013</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223998; 295999</t>
+          <t>223470; 293469</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1806_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,03</t>
+          <t>0,49; 1,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,8</t>
+          <t>2,14; 4,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,03</t>
+          <t>1,53; 2,91</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,98</t>
+          <t>0,72; 2,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,06</t>
+          <t>2,14; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,57</t>
+          <t>1,61; 2,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,7</t>
+          <t>2,23; 5,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,12</t>
+          <t>4,98; 7,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,64</t>
+          <t>3,9; 5,97</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,12</t>
+          <t>2,43; 4,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 8,89</t>
+          <t>6,77; 9,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,76</t>
+          <t>5,06; 6,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,86</t>
+          <t>1,84; 2,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,65</t>
+          <t>4,59; 5,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,12</t>
+          <t>3,4; 4,19</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>30063</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3593; 12931</t>
+          <t>3364; 12986</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14697; 32420</t>
+          <t>15720; 35102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20731; 39672</t>
+          <t>21845; 41434</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42263</t>
+          <t>44485</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5236; 23654</t>
+          <t>7604; 23798</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21659; 38865</t>
+          <t>22948; 40654</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26822; 55210</t>
+          <t>34192; 58347</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26117</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>78001</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16876; 40138</t>
+          <t>17926; 41198</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21813; 66458</t>
+          <t>40410; 64512</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47337; 92377</t>
+          <t>63005; 96452</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>82619</t>
+          <t>89756</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116192</t>
+          <t>123530</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23914; 47475</t>
+          <t>24025; 46673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63903; 97241</t>
+          <t>75690; 104941</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97683; 136690</t>
+          <t>106704; 144954</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>259023</t>
+          <t>276079</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58876; 98977</t>
+          <t>65067; 102269</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>144518; 207013</t>
+          <t>171546; 218572</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223470; 293469</t>
+          <t>246892; 304186</t>
         </is>
       </c>
     </row>
